--- a/기초율_v0.xlsx
+++ b/기초율_v0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\IPS\아이엠증권\업로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InKyoung\ALM\기초지수\20251118\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2D3DDB-02D3-4BF8-903E-C1D384C84562}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E66A170-4E65-42E0-A236-63CE8D6D8177}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2481,7 +2481,7 @@
         <v>0.39444000000000001</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2489,7 +2489,7 @@
         <v>4.4741000000000003E-2</v>
       </c>
       <c r="G2" s="2">
-        <v>6.0942550805944018E-2</v>
+        <v>2.8257000000000001E-2</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0.37758000000000003</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -2519,7 +2519,7 @@
         <v>3.7779E-2</v>
       </c>
       <c r="G3" s="4">
-        <v>5.7443182403278614E-2</v>
+        <v>2.7481999999999999E-2</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0.3594</v>
       </c>
       <c r="C4" s="4">
-        <v>1.9671999999999999E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2549,7 +2549,7 @@
         <v>3.3617000000000001E-2</v>
       </c>
       <c r="G4" s="4">
-        <v>5.4321495609240822E-2</v>
+        <v>2.6747E-2</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>0.34000999999999998</v>
       </c>
       <c r="C5" s="4">
-        <v>3.9343999999999997E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2579,7 +2579,7 @@
         <v>3.4112000000000003E-2</v>
       </c>
       <c r="G5" s="4">
-        <v>5.1523859775112868E-2</v>
+        <v>2.6048999999999999E-2</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0.32013000000000003</v>
       </c>
       <c r="C6" s="6">
-        <v>6.5573999999999993E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2609,7 +2609,7 @@
         <v>3.9507E-2</v>
       </c>
       <c r="G6" s="6">
-        <v>4.8998132306486086E-2</v>
+        <v>2.5388999999999998E-2</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0.30044999999999999</v>
       </c>
       <c r="C7" s="2">
-        <v>9.8361000000000004E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2639,7 +2639,7 @@
         <v>4.7413999999999998E-2</v>
       </c>
       <c r="G7" s="2">
-        <v>4.6710502902528317E-2</v>
+        <v>2.4760000000000001E-2</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>0.28140999999999999</v>
       </c>
       <c r="C8" s="4">
-        <v>0.123588</v>
+        <v>0.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2669,7 +2669,7 @@
         <v>5.3707999999999999E-2</v>
       </c>
       <c r="G8" s="4">
-        <v>4.4626000000000055E-2</v>
+        <v>2.4160999999999998E-2</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0.26273999999999997</v>
       </c>
       <c r="C9" s="4">
-        <v>0.14125699999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -2699,7 +2699,7 @@
         <v>5.5138E-2</v>
       </c>
       <c r="G9" s="4">
-        <v>4.2718638058022673E-2</v>
+        <v>2.3591999999999998E-2</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>0.24374000000000001</v>
       </c>
       <c r="C10" s="4">
-        <v>0.151366</v>
+        <v>0.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2729,7 +2729,7 @@
         <v>5.0793999999999999E-2</v>
       </c>
       <c r="G10" s="4">
-        <v>4.0969436796477687E-2</v>
+        <v>2.3047999999999999E-2</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0.22386</v>
       </c>
       <c r="C11" s="6">
-        <v>0.153916</v>
+        <v>0.2</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2759,7 +2759,7 @@
         <v>4.2688999999999998E-2</v>
       </c>
       <c r="G11" s="6">
-        <v>3.9356120637423553E-2</v>
+        <v>2.2527999999999999E-2</v>
       </c>
       <c r="H11" s="6">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>0.20274</v>
       </c>
       <c r="C12" s="2">
-        <v>0.14890700000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -2789,7 +2789,7 @@
         <v>3.4550999999999998E-2</v>
       </c>
       <c r="G12" s="2">
-        <v>3.7866715542273166E-2</v>
+        <v>2.2032E-2</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>0.18049999999999999</v>
       </c>
       <c r="C13" s="4">
-        <v>0.14571899999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2819,7 +2819,7 @@
         <v>2.9843999999999999E-2</v>
       </c>
       <c r="G13" s="4">
-        <v>3.6484325434459786E-2</v>
+        <v>2.1557E-2</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>0.15892000000000001</v>
       </c>
       <c r="C14" s="4">
-        <v>0.14435000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2849,7 +2849,7 @@
         <v>2.8804E-2</v>
       </c>
       <c r="G14" s="4">
-        <v>3.5200863259641224E-2</v>
+        <v>2.1101999999999999E-2</v>
       </c>
       <c r="H14" s="4">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0.14137</v>
       </c>
       <c r="C15" s="4">
-        <v>0.14480299999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2879,7 +2879,7 @@
         <v>3.1189999999999999E-2</v>
       </c>
       <c r="G15" s="4">
-        <v>3.4003134765186127E-2</v>
+        <v>2.0666E-2</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
@@ -2901,7 +2901,7 @@
         <v>0.12687000000000001</v>
       </c>
       <c r="C16" s="6">
-        <v>0.14707600000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2909,7 +2909,7 @@
         <v>3.5485999999999997E-2</v>
       </c>
       <c r="G16" s="6">
-        <v>3.2885680513837778E-2</v>
+        <v>2.0247999999999999E-2</v>
       </c>
       <c r="H16" s="6">
         <v>0</v>
@@ -2931,7 +2931,7 @@
         <v>0.11516</v>
       </c>
       <c r="C17" s="2">
-        <v>0.15117</v>
+        <v>0.2</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -2939,7 +2939,7 @@
         <v>4.0070000000000001E-2</v>
       </c>
       <c r="G17" s="2">
-        <v>3.18379315511228E-2</v>
+        <v>1.9845000000000002E-2</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -2961,7 +2961,7 @@
         <v>0.10564999999999999</v>
       </c>
       <c r="C18" s="4">
-        <v>0.15209400000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -2969,7 +2969,7 @@
         <v>4.3756999999999997E-2</v>
       </c>
       <c r="G18" s="4">
-        <v>3.0856245959391515E-2</v>
+        <v>1.9460000000000002E-2</v>
       </c>
       <c r="H18" s="4">
         <v>0</v>
@@ -2991,7 +2991,7 @@
         <v>9.7820000000000004E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>0.14985000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2999,7 +2999,7 @@
         <v>4.5081999999999997E-2</v>
       </c>
       <c r="G19" s="4">
-        <v>2.9931966401074428E-2</v>
+        <v>1.9088000000000001E-2</v>
       </c>
       <c r="H19" s="4">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>9.1300000000000006E-2</v>
       </c>
       <c r="C20" s="4">
-        <v>0.14443600000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -3029,7 +3029,7 @@
         <v>4.3841999999999999E-2</v>
       </c>
       <c r="G20" s="4">
-        <v>2.9062732415243042E-2</v>
+        <v>1.8731000000000001E-2</v>
       </c>
       <c r="H20" s="4">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>8.584E-2</v>
       </c>
       <c r="C21" s="6">
-        <v>0.135854</v>
+        <v>0.2</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -3059,7 +3059,7 @@
         <v>4.0321000000000003E-2</v>
       </c>
       <c r="G21" s="6">
-        <v>2.8241311485369458E-2</v>
+        <v>1.8386E-2</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>8.1390000000000004E-2</v>
       </c>
       <c r="C22" s="2">
-        <v>0.124102</v>
+        <v>0.2</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -3089,7 +3089,7 @@
         <v>3.5786999999999999E-2</v>
       </c>
       <c r="G22" s="2">
-        <v>2.74662611085843E-2</v>
+        <v>1.8055000000000002E-2</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>7.7700000000000005E-2</v>
       </c>
       <c r="C23" s="4">
-        <v>0.115868</v>
+        <v>0.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -3119,7 +3119,7 @@
         <v>3.1580999999999998E-2</v>
       </c>
       <c r="G23" s="4">
-        <v>2.6731433110316782E-2</v>
+        <v>1.7734E-2</v>
       </c>
       <c r="H23" s="4">
         <v>0</v>
@@ -3141,7 +3141,7 @@
         <v>7.4550000000000005E-2</v>
       </c>
       <c r="C24" s="4">
-        <v>0.111151</v>
+        <v>0.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -3149,7 +3149,7 @@
         <v>2.9406000000000002E-2</v>
       </c>
       <c r="G24" s="4">
-        <v>2.6036051173623509E-2</v>
+        <v>1.7425E-2</v>
       </c>
       <c r="H24" s="4">
         <v>0</v>
@@ -3171,7 +3171,7 @@
         <v>7.177E-2</v>
       </c>
       <c r="C25" s="4">
-        <v>0.109953</v>
+        <v>0.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -3179,7 +3179,7 @@
         <v>2.9304E-2</v>
       </c>
       <c r="G25" s="4">
-        <v>2.5374807947531997E-2</v>
+        <v>1.7127E-2</v>
       </c>
       <c r="H25" s="4">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>6.93E-2</v>
       </c>
       <c r="C26" s="6">
-        <v>0.112271</v>
+        <v>0.2</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3209,7 +3209,7 @@
         <v>2.9904E-2</v>
       </c>
       <c r="G26" s="6">
-        <v>2.4747415651329208E-2</v>
+        <v>1.6839E-2</v>
       </c>
       <c r="H26" s="6">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>6.7080000000000001E-2</v>
       </c>
       <c r="C27" s="2">
-        <v>0.118107</v>
+        <v>0.2</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -3239,7 +3239,7 @@
         <v>2.9125999999999999E-2</v>
       </c>
       <c r="G27" s="2">
-        <v>2.4149230065723781E-2</v>
+        <v>1.6559000000000001E-2</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>6.5180000000000002E-2</v>
       </c>
       <c r="C28" s="4">
-        <v>0.12177399999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -3269,7 +3269,7 @@
         <v>2.6894000000000001E-2</v>
       </c>
       <c r="G28" s="4">
-        <v>2.3580324542538778E-2</v>
+        <v>1.6289999999999999E-2</v>
       </c>
       <c r="H28" s="4">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>6.3780000000000003E-2</v>
       </c>
       <c r="C29" s="4">
-        <v>0.12327200000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -3299,7 +3299,7 @@
         <v>2.5512E-2</v>
       </c>
       <c r="G29" s="4">
-        <v>2.3036585970215961E-2</v>
+        <v>1.6029000000000002E-2</v>
       </c>
       <c r="H29" s="4">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>6.2960000000000002E-2</v>
       </c>
       <c r="C30" s="4">
-        <v>0.122601</v>
+        <v>0.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -3329,7 +3329,7 @@
         <v>2.6360999999999999E-2</v>
       </c>
       <c r="G30" s="4">
-        <v>2.2518356148899965E-2</v>
+        <v>1.5775000000000001E-2</v>
       </c>
       <c r="H30" s="4">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>6.2719999999999998E-2</v>
       </c>
       <c r="C31" s="6">
-        <v>0.11976000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -3359,7 +3359,7 @@
         <v>2.9350999999999999E-2</v>
       </c>
       <c r="G31" s="6">
-        <v>2.202195335836632E-2</v>
+        <v>1.5531E-2</v>
       </c>
       <c r="H31" s="6">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="C32" s="2">
-        <v>0.11475</v>
+        <v>0.2</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -3389,7 +3389,7 @@
         <v>3.2825E-2</v>
       </c>
       <c r="G32" s="2">
-        <v>2.1547919567824758E-2</v>
+        <v>1.5292999999999999E-2</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -3411,7 +3411,7 @@
         <v>6.3589999999999994E-2</v>
       </c>
       <c r="C33" s="4">
-        <v>0.109712</v>
+        <v>0.2</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -3419,7 +3419,7 @@
         <v>3.4724999999999999E-2</v>
       </c>
       <c r="G33" s="4">
-        <v>2.1092927996188449E-2</v>
+        <v>1.5062000000000001E-2</v>
       </c>
       <c r="H33" s="4">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>6.4320000000000002E-2</v>
       </c>
       <c r="C34" s="4">
-        <v>0.104646</v>
+        <v>0.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -3449,7 +3449,7 @@
         <v>3.3639000000000002E-2</v>
       </c>
       <c r="G34" s="4">
-        <v>2.0657669922597321E-2</v>
+        <v>1.4840000000000001E-2</v>
       </c>
       <c r="H34" s="4">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>6.4729999999999996E-2</v>
       </c>
       <c r="C35" s="4">
-        <v>9.9553000000000003E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -3479,7 +3479,7 @@
         <v>2.9506000000000001E-2</v>
       </c>
       <c r="G35" s="4">
-        <v>2.0239114077851506E-2</v>
+        <v>1.4623000000000001E-2</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>6.4879999999999993E-2</v>
       </c>
       <c r="C36" s="6">
-        <v>9.4432000000000002E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -3509,7 +3509,7 @@
         <v>2.3709999999999998E-2</v>
       </c>
       <c r="G36" s="6">
-        <v>1.9838062799342415E-2</v>
+        <v>1.4411999999999999E-2</v>
       </c>
       <c r="H36" s="6">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>6.5629999999999994E-2</v>
       </c>
       <c r="C37" s="2">
-        <v>8.9283000000000001E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -3539,7 +3539,7 @@
         <v>1.8221000000000001E-2</v>
       </c>
       <c r="G37" s="2">
-        <v>1.9451733547211525E-2</v>
+        <v>1.4206E-2</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>6.7790000000000003E-2</v>
       </c>
       <c r="C38" s="4">
-        <v>9.2293E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3569,7 +3569,7 @@
         <v>1.5063E-2</v>
       </c>
       <c r="G38" s="4">
-        <v>1.9081010704367518E-2</v>
+        <v>1.4008E-2</v>
       </c>
       <c r="H38" s="4">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>7.2749999999999995E-2</v>
       </c>
       <c r="C39" s="4">
-        <v>0.103463</v>
+        <v>0.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -3599,7 +3599,7 @@
         <v>1.4404999999999999E-2</v>
       </c>
       <c r="G39" s="4">
-        <v>1.8723323197914254E-2</v>
+        <v>1.3814999999999999E-2</v>
       </c>
       <c r="H39" s="4">
         <v>0</v>
@@ -3621,7 +3621,7 @@
         <v>7.7619999999999995E-2</v>
       </c>
       <c r="C40" s="4">
-        <v>0.122792</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3629,7 +3629,7 @@
         <v>1.5048000000000001E-2</v>
       </c>
       <c r="G40" s="4">
-        <v>1.8379615290838203E-2</v>
+        <v>1.3625999999999999E-2</v>
       </c>
       <c r="H40" s="4">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>8.233E-2</v>
       </c>
       <c r="C41" s="6">
-        <v>0.150281</v>
+        <v>0.2</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -3659,7 +3659,7 @@
         <v>1.5374000000000001E-2</v>
       </c>
       <c r="G41" s="6">
-        <v>1.804749737325495E-2</v>
+        <v>1.3443E-2</v>
       </c>
       <c r="H41" s="6">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>9.4350000000000003E-2</v>
       </c>
       <c r="C42" s="2">
-        <v>0.18592900000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -3689,7 +3689,7 @@
         <v>1.5146E-2</v>
       </c>
       <c r="G42" s="2">
-        <v>1.7727956549702606E-2</v>
+        <v>1.3265000000000001E-2</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>0.11796</v>
       </c>
       <c r="C43" s="4">
-        <v>0.214448</v>
+        <v>0.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3719,7 +3719,7 @@
         <v>1.4914999999999999E-2</v>
       </c>
       <c r="G43" s="4">
-        <v>1.7418760268286038E-2</v>
+        <v>1.3091E-2</v>
       </c>
       <c r="H43" s="4">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0.15145</v>
       </c>
       <c r="C44" s="4">
-        <v>0.23583699999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3749,7 +3749,7 @@
         <v>1.4696000000000001E-2</v>
       </c>
       <c r="G44" s="4">
-        <v>1.7120925311085555E-2</v>
+        <v>1.2921999999999999E-2</v>
       </c>
       <c r="H44" s="4">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>0.18717</v>
       </c>
       <c r="C45" s="4">
-        <v>0.25722499999999998</v>
+        <v>0.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -3779,7 +3779,7 @@
         <v>1.4487999999999999E-2</v>
       </c>
       <c r="G45" s="4">
-        <v>1.6832356145120686E-2</v>
+        <v>1.2756999999999999E-2</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0.21614</v>
       </c>
       <c r="C46" s="6">
-        <v>0.25722499999999998</v>
+        <v>0.2</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -3809,7 +3809,7 @@
         <v>1.4276E-2</v>
       </c>
       <c r="G46" s="6">
-        <v>1.6554089018754992E-2</v>
+        <v>1.2596E-2</v>
       </c>
       <c r="H46" s="6">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>0.23258999999999999</v>
       </c>
       <c r="C47" s="2">
-        <v>0.31501600000000002</v>
+        <v>0.2</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -3839,7 +3839,7 @@
         <v>1.4076E-2</v>
       </c>
       <c r="G47" s="2">
-        <v>1.6284148817962363E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>0.23488000000000001</v>
       </c>
       <c r="C48" s="4">
-        <v>0.34532400000000002</v>
+        <v>0.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3869,7 +3869,8 @@
         <v>1.3885E-2</v>
       </c>
       <c r="G48" s="4">
-        <v>1.6023583313584888E-2</v>
+        <f t="shared" ref="G48:G83" si="1">G47</f>
+        <v>1.244E-2</v>
       </c>
       <c r="H48" s="4">
         <v>0</v>
@@ -3891,7 +3892,7 @@
         <v>0.22672</v>
       </c>
       <c r="C49" s="4">
-        <v>0.38185999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -3899,7 +3900,8 @@
         <v>1.3690000000000001E-2</v>
       </c>
       <c r="G49" s="4">
-        <v>1.5770523945398018E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H49" s="4">
         <v>0</v>
@@ -3921,7 +3923,7 @@
         <v>0.21535000000000001</v>
       </c>
       <c r="C50" s="4">
-        <v>0.41017700000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3929,7 +3931,8 @@
         <v>1.3505E-2</v>
       </c>
       <c r="G50" s="4">
-        <v>1.5526023816125889E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H50" s="4">
         <v>0</v>
@@ -3951,7 +3954,7 @@
         <v>0.20813000000000001</v>
       </c>
       <c r="C51" s="6">
-        <v>0.43990699999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -3959,7 +3962,8 @@
         <v>1.3329000000000001E-2</v>
       </c>
       <c r="G51" s="6">
-        <v>1.5288309248322252E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H51" s="6">
         <v>0</v>
@@ -3981,7 +3985,7 @@
         <v>0.20924999999999999</v>
       </c>
       <c r="C52" s="2">
-        <v>0.471049</v>
+        <v>0.2</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -3989,7 +3993,8 @@
         <v>1.315E-2</v>
       </c>
       <c r="G52" s="2">
-        <v>1.505843384999328E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -4011,7 +4016,7 @@
         <v>0.21728</v>
       </c>
       <c r="C53" s="4">
-        <v>0.47462900000000002</v>
+        <v>0.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4019,7 +4024,8 @@
         <v>1.2978999999999999E-2</v>
       </c>
       <c r="G53" s="4">
-        <v>1.4834708930544727E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H53" s="4">
         <v>0</v>
@@ -4041,7 +4047,7 @@
         <v>0.22489999999999999</v>
       </c>
       <c r="C54" s="4">
-        <v>0.45064799999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4049,7 +4055,8 @@
         <v>1.2817E-2</v>
       </c>
       <c r="G54" s="4">
-        <v>1.4618184843746773E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H54" s="4">
         <v>0</v>
@@ -4071,7 +4078,7 @@
         <v>0.23077</v>
       </c>
       <c r="C55" s="4">
-        <v>0.35643799999999998</v>
+        <v>0.2</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -4079,7 +4086,8 @@
         <v>1.2651000000000001E-2</v>
       </c>
       <c r="G55" s="4">
-        <v>1.4407249437350611E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H55" s="4">
         <v>0</v>
@@ -4101,7 +4109,7 @@
         <v>0.23855999999999999</v>
       </c>
       <c r="C56" s="6">
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -4109,7 +4117,8 @@
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G56" s="6">
-        <v>1.4202946890284673E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H56" s="6">
         <v>0</v>
@@ -4131,8 +4140,7 @@
         <v>0.24864</v>
       </c>
       <c r="C57" s="2">
-        <f>C56</f>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -4141,8 +4149,8 @@
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G57" s="2">
-        <f t="shared" ref="G57:G83" si="1">G56</f>
-        <v>1.4202946890284673E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.244E-2</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -4165,8 +4173,7 @@
         <v>0.24864</v>
       </c>
       <c r="C58" s="4">
-        <f t="shared" ref="C58:C83" si="2">C57</f>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -4176,7 +4183,7 @@
       </c>
       <c r="G58" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H58" s="4">
         <v>0</v>
@@ -4197,33 +4204,32 @@
         <v>72</v>
       </c>
       <c r="B59" s="4">
-        <f t="shared" ref="B59:B61" si="3">B58</f>
+        <f t="shared" ref="B59:B61" si="2">B58</f>
         <v>0.24864</v>
       </c>
       <c r="C59" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4">
-        <f t="shared" ref="F59:F61" si="4">F58</f>
+        <f t="shared" ref="F59:F61" si="3">F58</f>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G59" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H59" s="4">
         <v>0</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4">
-        <f t="shared" ref="J59:K61" si="5">J58</f>
+        <f t="shared" ref="J59:K61" si="4">J58</f>
         <v>1.08E-3</v>
       </c>
       <c r="K59" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4233,33 +4239,32 @@
         <v>73</v>
       </c>
       <c r="B60" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.24864</v>
       </c>
       <c r="C60" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G60" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H60" s="4">
         <v>0</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.08E-3</v>
       </c>
       <c r="K60" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4269,33 +4274,32 @@
         <v>74</v>
       </c>
       <c r="B61" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.24864</v>
       </c>
       <c r="C61" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G61" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H61" s="4">
         <v>0</v>
       </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.08E-3</v>
       </c>
       <c r="K61" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4305,33 +4309,32 @@
         <v>75</v>
       </c>
       <c r="B62" s="2">
-        <f t="shared" ref="B62:K63" si="6">B61</f>
+        <f t="shared" ref="B62:K63" si="5">B61</f>
         <v>0.24864</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G62" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.08E-3</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4341,33 +4344,32 @@
         <v>76</v>
       </c>
       <c r="B63" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.24864</v>
       </c>
       <c r="C63" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G63" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H63" s="4">
         <v>0</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.08E-3</v>
       </c>
       <c r="K63" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4377,33 +4379,32 @@
         <v>77</v>
       </c>
       <c r="B64" s="4">
-        <f t="shared" ref="B64:B66" si="7">B63</f>
+        <f t="shared" ref="B64:B66" si="6">B63</f>
         <v>0.24864</v>
       </c>
       <c r="C64" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4">
-        <f t="shared" ref="F64:F66" si="8">F63</f>
+        <f t="shared" ref="F64:F66" si="7">F63</f>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G64" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H64" s="4">
         <v>0</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4">
-        <f t="shared" ref="J64:K71" si="9">J63</f>
+        <f t="shared" ref="J64:K71" si="8">J63</f>
         <v>1.08E-3</v>
       </c>
       <c r="K64" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4413,33 +4414,32 @@
         <v>78</v>
       </c>
       <c r="B65" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.24864</v>
       </c>
       <c r="C65" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G65" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H65" s="4">
         <v>0</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.08E-3</v>
       </c>
       <c r="K65" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4449,33 +4449,32 @@
         <v>79</v>
       </c>
       <c r="B66" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.24864</v>
       </c>
       <c r="C66" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.2493000000000001E-2</v>
       </c>
       <c r="G66" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H66" s="4">
         <v>0</v>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.08E-3</v>
       </c>
       <c r="K66" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
@@ -4489,8 +4488,7 @@
         <v>0.24864</v>
       </c>
       <c r="C67" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -4499,7 +4497,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -4514,7 +4512,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <f t="shared" ref="A68:A83" si="10">+A67+1</f>
+        <f t="shared" ref="A68:A83" si="9">+A67+1</f>
         <v>81</v>
       </c>
       <c r="B68" s="4">
@@ -4522,8 +4520,7 @@
         <v>0.24864</v>
       </c>
       <c r="C68" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -4532,7 +4529,7 @@
       </c>
       <c r="G68" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H68" s="4">
         <v>0</v>
@@ -4549,16 +4546,15 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="B69" s="4">
-        <f t="shared" ref="B69:B71" si="11">B68</f>
+        <f t="shared" ref="B69:B71" si="10">B68</f>
         <v>0.24864</v>
       </c>
       <c r="C69" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -4567,33 +4563,32 @@
       </c>
       <c r="G69" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H69" s="4">
         <v>0</v>
       </c>
       <c r="I69" s="4"/>
       <c r="J69" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.08E-3</v>
       </c>
       <c r="K69" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
+        <f t="shared" si="9"/>
+        <v>83</v>
+      </c>
+      <c r="B70" s="4">
         <f t="shared" si="10"/>
-        <v>83</v>
-      </c>
-      <c r="B70" s="4">
-        <f t="shared" si="11"/>
         <v>0.24864</v>
       </c>
       <c r="C70" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -4602,33 +4597,32 @@
       </c>
       <c r="G70" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H70" s="4">
         <v>0</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.08E-3</v>
       </c>
       <c r="K70" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
+        <f t="shared" si="9"/>
+        <v>84</v>
+      </c>
+      <c r="B71" s="4">
         <f t="shared" si="10"/>
-        <v>84</v>
-      </c>
-      <c r="B71" s="4">
-        <f t="shared" si="11"/>
         <v>0.24864</v>
       </c>
       <c r="C71" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -4637,32 +4631,31 @@
       </c>
       <c r="G71" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H71" s="4">
         <v>0</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.08E-3</v>
       </c>
       <c r="K71" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6E-4</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="B72" s="2">
         <v>0.21979000000000001</v>
       </c>
       <c r="C72" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -4671,7 +4664,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -4686,15 +4679,14 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="B73" s="2">
         <v>0.21979000000000001</v>
       </c>
       <c r="C73" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -4703,7 +4695,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -4718,15 +4710,14 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="B74" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C74" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -4735,7 +4726,7 @@
       </c>
       <c r="G74" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H74" s="4">
         <v>0</v>
@@ -4750,15 +4741,14 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="B75" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C75" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -4767,7 +4757,7 @@
       </c>
       <c r="G75" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H75" s="4">
         <v>0</v>
@@ -4782,15 +4772,14 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="B76" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C76" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -4799,7 +4788,7 @@
       </c>
       <c r="G76" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H76" s="4">
         <v>0</v>
@@ -4814,15 +4803,14 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="B77" s="6">
         <v>0.21979000000000001</v>
       </c>
       <c r="C77" s="6">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -4831,7 +4819,7 @@
       </c>
       <c r="G77" s="6">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H77" s="6">
         <v>0</v>
@@ -4846,15 +4834,14 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="B78" s="2">
         <v>0.21979000000000001</v>
       </c>
       <c r="C78" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -4863,7 +4850,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -4878,15 +4865,14 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="B79" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C79" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -4895,7 +4881,7 @@
       </c>
       <c r="G79" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H79" s="4">
         <v>0</v>
@@ -4910,15 +4896,14 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>93</v>
       </c>
       <c r="B80" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C80" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -4927,7 +4912,7 @@
       </c>
       <c r="G80" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H80" s="4">
         <v>0</v>
@@ -4942,15 +4927,14 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="B81" s="4">
         <v>0.21979000000000001</v>
       </c>
       <c r="C81" s="4">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -4959,7 +4943,7 @@
       </c>
       <c r="G81" s="4">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H81" s="4">
         <v>0</v>
@@ -4974,15 +4958,14 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="B82" s="6">
         <v>0.21979000000000001</v>
       </c>
       <c r="C82" s="6">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -4991,7 +4974,7 @@
       </c>
       <c r="G82" s="6">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H82" s="6">
         <v>0</v>
@@ -5006,15 +4989,14 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="B83" s="2">
         <v>0.21979000000000001</v>
       </c>
       <c r="C83" s="2">
-        <f t="shared" si="2"/>
-        <v>0.25600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -5023,7 +5005,7 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="1"/>
-        <v>1.4202946890284673E-2</v>
+        <v>1.244E-2</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
